--- a/帝国时代2决定版 文明联盟 箭塔流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 箭塔流最优研究顺序 By RemonBo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开局3免费位" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续2000金顺序" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="甲类·塔本体强化" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·石料与建造" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·减费用与资源效率" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="与箭塔无关·可跳过" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主选文明推荐" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全62文明总名次" sheetId="7" state="visible" r:id="rId7"/>
@@ -20,10 +20,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$G$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·塔本体强化'!$A$1:$E$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·塔本体强化'!$A$1:$E$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·塔本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·石料与建造'!$A$1:$E$22</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·石料与建造'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与箭塔无关·可跳过'!$A$1:$C$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与箭塔无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$19</definedName>
@@ -90,7 +90,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -104,17 +104,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFE9CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -125,6 +115,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EAF1FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -159,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -203,28 +198,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -233,16 +207,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -932,7 +912,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -952,147 +932,147 @@
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>**付费第一顺位**：一旦进入城堡时代，这是全表最强的塔本体乘区。如果你打的是长期局，甚至可以把它提到免费位。</t>
+          <t>【阶段1·本体强化】**付费第一顺位**：一旦进入城堡时代，这是全表最强的塔本体乘区。如果你打的是长期局，甚至可以把它提到免费位。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="66" customHeight="1">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>条顿</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>塔驻扎容量 +5；开垛口</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>需真的驻军</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>农田费用-40%；TC驻扎容量+10；塔驻扎容量+5；步兵/骑兵城堡/帝王近战护甲+1/+2；僧侣治疗范围+100%；近射孔/草药免费；重装甲（攻城武器近战护甲+4）；开垛口（城堡射程+3；驻扎的步兵射箭）；单位更难被招降</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>把「塔」变成「要塞」——驻满农民后单塔箭数上一个台阶；同卡城堡线拿到射程 +3。</t>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>【阶段1·本体强化】把「塔」变成「要塞」——驻满农民后单塔箭数上一个台阶；同卡城堡线拿到射程 +3。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>高丽</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>塔升级免费；邑城（射程+2）；石矿工+20%</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>无条件（升级炮塔需化学）</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>石矿工速度+20%；远程/步兵木材费用-50%；弓兵护甲/塔升级免费（升级炮塔需要化学）；战船木材-20%；邑城（瞭望箭塔系射程+2）；神机箭（火箭推车/龟甲船射程+1，可发额外炮弹）；村民视野 +3</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>一卡三吃：升级不花石料、射程 +2 能先手压制对方塔与城镇中心、石料产能 +20%。</t>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>【阶段1·本体强化】一卡三吃：升级不花石料、射程 +2 能先手压制对方塔与城镇中心、石料产能 +20%。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>不列颠</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>英皇侍卫（瞭望箭塔系攻 +2）</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>无条件</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>羊倌工作速度+25%；城堡起TC木材费用-50%；步弓手城堡/帝王射程+1/+2；英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）；战狼号（巨型投石机可造成爆炸伤害且更准）；靶场工作速度 +10%</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>塔基础箭伤低，+2 的相对收益远高于它给其他兵种的收益。</t>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>【阶段1·本体强化】塔基础箭伤低，+2 的相对收益远高于它给其他兵种的收益。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="81" customHeight="1">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>女真</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>加固堡垒（防御工事每分钟回 500 生命）；防御工事升级木材-75%、研究+100%</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>无条件</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>猎物/牲畜肉不腐烂；封建起骑乘/火枪骑攻速+25%；城堡可用攻城工程技师；攻城/防御工事升级木材-75%，研究+100%；友军误伤-50%；加固堡垒（防御工事每分钟回500生命）；霹雳炸弹（火箭推车/掷弹兵/楼船被击败时爆炸；炮弹额外爆炸）；火药单位视野 +2</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>**拆不掉 = 不用重建**。配合升级降价，是「守成型塔推」的支柱。</t>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>【阶段1·本体强化】**拆不掉 = 不用重建**。配合升级降价，是「守成型塔推」的支柱。</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1087,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -1127,742 +1107,742 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>与上面的回血互为补充：一个加血上限，一个加回复速度。</t>
+          <t>【阶段1·本体强化】与上面的回血互为补充：一个加血上限，一个加回复速度。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="81" customHeight="1">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>拜占庭</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>炮塔爆炸范围提升；建筑生命 +40%</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>炮塔部分偏后期</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>建筑黑暗/封建/城堡/帝王生命+10/20/30/40%；骆驼/掷矛/长矛兵费用-25%；城镇瞭望/巡逻免费；升帝王费用-33%；喷火/德罗蒙攻速+25%；希腊之火（喷火船射程+1；德罗蒙和炮塔爆炸范围提升）；后勤学（甲胄骑兵和瓦兰吉卫队可造成践踏伤害）；僧侣治疗速度 +100%</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>【阶段1·本体强化】炮塔专属加成 + 全家建筑耐久。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="66" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>防御工事造成中毒伤害；塔/城堡提供人口 +10</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>开局每种资源+25；村民可驻聚落；战败单位返15%成本；靶场/兵营升级食物-50%；卡西克（蔷琵战士/投石手攻速+25%）；箭毒（步弓手/防御工事造成中毒伤害）；塔楼和城堡提供的人口空间 +10</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>【阶段1·本体强化】中毒是持续伤害，配合拆家更稳；人口 +10 解放前线补农民的房屋位。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="66" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>罗斯堡垒（40% 石料 → 木材）</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>农民工作速度+15%；纵火/软甲免费；攻城武器厂单位费用-15%；僧侣移速+20%；罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）；皇家卫队（步兵可造成践踏伤害）；军事建筑 (城堡除外) 提供的人口空间 +5</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>【阶段2·减费用】石料瓶颈的唯一解。理论上越早越好；如果你已经靠前置把塔立满，边际收益下降。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="81" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>建筑石料 -15%</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>房屋/聚落人口+5；建筑石料-15%；军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%；城堡起步兵铁匠铺升级影响村民；安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）；织物盾（印加枪兵长/投石手/蔷琵战士近战护甲+1/远程护甲+1）；开始游戏时额外获得一只羊驼</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>【阶段2·减费用】成本类收益，越晚买边际越低。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="51" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>TC 石料 -50%；城堡时代可建营垒</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>民兵系升级免费；铁匠铺/攻城武器厂科技食物费用-50%；TC石料费用-50%；城堡时代可建营垒；马镫（骑兵攻速+33%）；协议（民兵系近战护甲+5）；铁匠铺工作速度 +80%</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>【阶段2·减费用】营垒提供第二种前压工事，价值取决于你是否会用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="51" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>城墙费用 -50%</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>开局村民+1，食物-50；资源持续+15%；步弓手封建/城堡/帝王费用-10/20/30%；胡尔切掷矛兵（掷矛手额外投掷一支长矛）；霍尔坎（鹰勇士生命+40）；城墙费用 -50%</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>【阶段2·减费用】圈地与护农，非塔本体。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="81" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>西西里</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>S-</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>防御工事建造 +50%（初始石料已失效）</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>无条件</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>初始石料+100；农田升级食物+125%；士兵额外受伤-40%；黑暗可建城楼（替瞭望塔系）；防御工事建造+50%，TC建造+100%；第一次十字军东征（每座TC产生5萨金特卫兵，最多5座；提升抗招降）；锁子甲（骑士系近战护甲+1/远程护甲+2）；运输船视野 +5 且费用 -50%</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>买晚了只剩建造速度，但建造速度本身就是塔推的胜负手之一，仍值 2000 金。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="66" customHeight="1">
-      <c r="A9" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>S-</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>罗斯堡垒（40% 石料 → 木材）</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>【阶段3·资源效率】买晚了只剩建造速度，但建造速度本身就是塔推的胜负手之一，仍值 2000 金。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="111" customHeight="1">
+      <c r="A15" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>普鲁人</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>石矿持续时间 +30%</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>无条件</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>农民工作速度+15%；纵火/软甲免费；攻城武器厂单位费用-15%；僧侣移速+20%；罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）；皇家卫队（步兵可造成践踏伤害）；军事建筑 (城堡除外) 提供的人口空间 +5</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>石料瓶颈的唯一解。理论上越早越好；如果你已经靠前置把塔立满，边际收益下降。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="66" customHeight="1">
-      <c r="A10" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>采石村民缓慢获食；石矿持续+30%；村民/捕鱼船采牡蛎+15%；附近无敌人时马厩单位每分钟回25生命（古典起）；每时代小艇费用-10%，受攻+1（市政起）；践踏屠戮（桑纳哈亚提升践踏伤害）；叶头箭杆（帕提尤达长弓兵提升近距伤害）；吠陀教义（翰林院每项科技使村民效率+2%，最大20%）；斯坎达瓦拉斯堡垒（堡垒可用炮台升级）；贸易车移动速度 +15%</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>【阶段3·资源效率】前置资源池的扩容，属于「锦上添花」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="66" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>石矿工产石料 + 黄金</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>大庄园替代磨坊；村民封建/城堡/帝王每分钟恢复10/15/20生命；石矿工产石料+黄金；血统/斥候食物费用-50%；贵族特权（骑士黄金费用-60%）；列克提克遗产（斥候系可造成践踏伤害）；斥候骑兵系对远程士兵的攻击力 +1</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>【阶段3·资源效率】石金双收，但需要你持续采石；塔推通常打不到那么久。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="81" customHeight="1">
+      <c r="A17" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>建筑工速度 +30%</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>建筑工速度+30%；研究科技获黄金+20；铁匠铺升级不耗金；火药单位攻速+18%；炮舰攻击移动目标更准；宗教法庭（僧侣/传教士招降快；传教士招降距离+1）；霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）；贸易单位产生的黄金 +25%</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>【阶段3·资源效率】与「防御工事建造 +50%」叠加后立塔极快，但单独买收益递减。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="81" customHeight="1">
+      <c r="A18" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>村民收集/建造/修理速度 +5%</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>村民收集/建造/修理速度+5%；步兵护甲升级效果加倍；蝎式弩黄金-50%；箭船系/德罗蒙战舰近战护甲+1/远程护甲+1；弩炮（蝎式弩攻速+33%；箭船系攻+2）；野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）；降低蝎式弩的最小射程</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>【阶段3·资源效率】稳定的小幅乘算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="66" customHeight="1">
+      <c r="A19" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>哨站视野 +3 且不消耗石料</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>升时代获得黄金+100、食物+100；步弓手攻击速度+18%；长枪兵升级免费；龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）；扭绞机（攻城武器厂单位爆炸伤害范围提升）；哨站视野 +3 且不消耗石料</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>【阶段3·资源效率】侦察与石料节约，锦上添花。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="66" customHeight="1">
+      <c r="A20" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>采矿场科技免费</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>采矿场科技免费；铁匠铺/大学木材费用-100；长矛兵系造成的额外伤害+25%；狂热/圣洁影响村民；城堡时代可用化学/火枪手；大车阵战术（火药单位移速+10%）；胡斯革新（僧侣和修道院科技消耗黄金而非食物）；市场效率 +80%</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>【阶段3·资源效率】纯石料前置，后期买几乎无用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="66" customHeight="1">
+      <c r="A21" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>土耳其</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>炮塔射程 +2；化学免费</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>需已解锁炮塔</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>金矿工速度+25%；斥候骑兵系远程护甲+1且升级免费；化学免费，火药技术成本-50%；火药单位生命+25%；西帕希骑兵（骑射手生命+20）；火炮术（炮塔/手推炮/炮舰射程+2）；火药单位训练速度 +25%</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>进入帝王、有炮塔之后的核心火力升级，属于「后期才有用」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="81" customHeight="1">
-      <c r="A11" s="14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>拜占庭</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>炮塔爆炸范围提升；建筑生命 +40%</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>炮塔部分偏后期</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>建筑黑暗/封建/城堡/帝王生命+10/20/30/40%；骆驼/掷矛/长矛兵费用-25%；城镇瞭望/巡逻免费；升帝王费用-33%；喷火/德罗蒙攻速+25%；希腊之火（喷火船射程+1；德罗蒙和炮塔爆炸范围提升）；后勤学（甲胄骑兵和瓦兰吉卫队可造成践踏伤害）；僧侣治疗速度 +100%</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>炮塔专属加成 + 全家建筑耐久。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="66" customHeight="1">
-      <c r="A12" s="14" t="n">
-        <v>14</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>防御工事造成中毒伤害；塔/城堡提供人口 +10</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>【阶段4·其他相关】进入帝王、有炮塔之后的核心火力升级，属于「后期才有用」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="96" customHeight="1">
+      <c r="A22" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>马其顿人</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>哨站可升级为强化哨站；世界尽头</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>无条件</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>开局每种资源+25；村民可驻聚落；战败单位返15%成本；靶场/兵营升级食物-50%；卡西克（蔷琵战士/投石手攻速+25%）；箭毒（步弓手/防御工事造成中毒伤害）；塔楼和城堡提供的人口空间 +10</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>中毒是持续伤害，配合拆家更稳；人口 +10 解放前线补农民的房屋位。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="81" customHeight="1">
-      <c r="A13" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>建筑石料 -15%</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>高地受伤-10%；兵营/靶场/马厩可用招募训令；步兵护甲升级适用于骑兵；攻城武器对建筑远程护甲+1，伤害+30%；老练千夫长（招募训令+33%）；世界尽头（强化哨站获更高光环和改进属性）；马其顿方阵步兵（方阵步兵最小攻击范围减半）；萨里沙骑兵（伙伴骑兵获快速冲锋）；哨站可以单独升级为强化哨站</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>【阶段4·其他相关】前哨网变成战力网，战术补充。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="81" customHeight="1">
+      <c r="A23" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>堡垒（城堡攻+4，额外受伤-25%）</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>无条件</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>房屋/聚落人口+5；建筑石料-15%；军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%；城堡起步兵铁匠铺升级影响村民；安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）；织物盾（印加枪兵长/投石手/蔷琵战士近战护甲+1/远程护甲+1）；开始游戏时额外获得一只羊驼</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>成本类收益，越晚买边际越低。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="111" customHeight="1">
-      <c r="A14" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>普鲁人</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>石矿持续时间 +30%</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>初始木材/食物+50；TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%；城堡时代可用帕提亚战术；帝王可建商队驿站；波斯步弓手（弓兵系消耗额外木材而非黄金）；堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）；骑士系对远程士兵的攻击力 +2</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>【阶段4·其他相关】偏城堡，箭塔不吃。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="66" customHeight="1">
+      <c r="A24" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>土堡（城堡工作速度 +25%）</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>无条件</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>采石村民缓慢获食；石矿持续+30%；村民/捕鱼船采牡蛎+15%；附近无敌人时马厩单位每分钟回25生命（古典起）；每时代小艇费用-10%，受攻+1（市政起）；践踏屠戮（桑纳哈亚提升践踏伤害）；叶头箭杆（帕提尤达长弓兵提升近距伤害）；吠陀教义（翰林院每项科技使村民效率+2%，最大20%）；斯坎达瓦拉斯堡垒（堡垒可用炮台升级）；贸易车移动速度 +15%</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>前置资源池的扩容，属于「锦上添花」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="66" customHeight="1">
-      <c r="A15" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>石矿工产石料 + 黄金</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>村民黑暗移速+5%，封建起+10%；马厩单位城堡/帝王费用-15/20%；船舰移速+10%；土堡（团队城堡工作速度+25%）；马格里布骆驼（骆驼每分钟恢复15生命）；从城堡时代开始，靶场提供标枪骑兵</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>【阶段4·其他相关】偏城堡。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="126" customHeight="1">
+      <c r="A25" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>无条件</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>大庄园替代磨坊；村民封建/城堡/帝王每分钟恢复10/15/20生命；石矿工产石料+黄金；血统/斥候食物费用-50%；贵族特权（骑士黄金费用-60%）；列克提克遗产（斥候系可造成践踏伤害）；斥候骑兵系对远程士兵的攻击力 +1</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>石金双收，但需要你持续采石；塔推通常打不到那么久。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="81" customHeight="1">
-      <c r="A16" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>西班牙</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>精锐掷矛手升级免费；市政/古典掷矛手每分钟回5/10生命；古典解锁战斗操练；任何高地可建除TC外所有建筑；堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点；羊倌/猎人采食时缓慢产金；奥多曼蒂突袭者（步兵/骑兵杀敌获金）；迪亚掠夺者（长矛兵系/征兵系/希腊步兵系/长柄逆刃刀战士摧毁建筑获木/食/金）；贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）；轻装盾兵（掷矛手造成穿透伤害）；建筑的视野 +3</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>【阶段4·其他相关】塔的经济外溢，非战力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="96" customHeight="1">
+      <c r="A26" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>建筑工速度 +30%</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>堡垒缓慢产出黄金</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>无条件</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>建筑工速度+30%；研究科技获黄金+20；铁匠铺升级不耗金；火药单位攻速+18%；炮舰攻击移动目标更准；宗教法庭（僧侣/传教士招降快；传教士招降距离+1）；霸权（村民生命+40，攻+6，近战护甲+2/远程护甲+2）；贸易单位产生的黄金 +25%</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>与「防御工事建造 +50%」叠加后立塔极快，但单独买收益递减。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="81" customHeight="1">
-      <c r="A17" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>进入市政/古典免费获一军事执政官；村民/捕鱼船存食+10%；古典解锁精锐希腊步兵；希洛人征兵（长矛/掷矛/村民训练+50%）；希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）；斯巴达特训（其他希腊步兵附近时希腊步兵+1/+1护甲）；伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）；兵营科技研究速度 +50%</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>【阶段4·其他相关】塔的经济外溢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="81" customHeight="1">
+      <c r="A27" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>村民收集/建造/修理速度 +5%</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>摧毁建筑抢夺 25% 资源</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>需主动拆家</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>捕鱼船/村民存食+5%；摧毁建筑抢25%资源；兵营/攻城武器厂黄金升级-66%；瓦兰吉/维京长船移速+10%；哈马思克（步兵失血时造成更多伤害）；北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）；攻城武器的视野 +2</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>【阶段4·其他相关】需要主动进攻拆家才生效。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="51" customHeight="1">
+      <c r="A28" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>蛮王（TC 无驻军也能射箭）</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>无条件</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>村民收集/建造/修理速度+5%；步兵护甲升级效果加倍；蝎式弩黄金-50%；箭船系/德罗蒙战舰近战护甲+1/远程护甲+1；弩炮（蝎式弩攻速+33%；箭船系攻+2）；野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）；降低蝎式弩的最小射程</t>
-        </is>
-      </c>
-      <c r="G17" s="19" t="inlineStr">
-        <is>
-          <t>稳定的小幅乘算。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="66" customHeight="1">
-      <c r="A18" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>哨站视野 +3 且不消耗石料</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>升时代获得黄金+100、食物+100；步弓手攻击速度+18%；长枪兵升级免费；龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）；扭绞机（攻城武器厂单位爆炸伤害范围提升）；哨站视野 +3 且不消耗石料</t>
-        </is>
-      </c>
-      <c r="G18" s="19" t="inlineStr">
-        <is>
-          <t>侦察与石料节约，锦上添花。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="96" customHeight="1">
-      <c r="A19" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>马其顿人</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>哨站可升级为强化哨站；世界尽头</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>高地受伤-10%；兵营/靶场/马厩可用招募训令；步兵护甲升级适用于骑兵；攻城武器对建筑远程护甲+1，伤害+30%；老练千夫长（招募训令+33%）；世界尽头（强化哨站获更高光环和改进属性）；马其顿方阵步兵（方阵步兵最小攻击范围减半）；萨里沙骑兵（伙伴骑兵获快速冲锋）；哨站可以单独升级为强化哨站</t>
-        </is>
-      </c>
-      <c r="G19" s="19" t="inlineStr">
-        <is>
-          <t>前哨网变成战力网，战术补充。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="51" customHeight="1">
-      <c r="A20" s="17" t="n">
-        <v>22</v>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>TC 石料 -50%；城堡时代可建营垒</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>民兵系升级免费；铁匠铺/攻城武器厂科技食物费用-50%；TC石料费用-50%；城堡时代可建营垒；马镫（骑兵攻速+33%）；协议（民兵系近战护甲+5）；铁匠铺工作速度 +80%</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>营垒提供第二种前压工事，价值取决于你是否会用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="66" customHeight="1">
-      <c r="A21" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>采矿场科技免费</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>采矿场科技免费；铁匠铺/大学木材费用-100；长矛兵系造成的额外伤害+25%；狂热/圣洁影响村民；城堡时代可用化学/火枪手；大车阵战术（火药单位移速+10%）；胡斯革新（僧侣和修道院科技消耗黄金而非食物）；市场效率 +80%</t>
-        </is>
-      </c>
-      <c r="G21" s="19" t="inlineStr">
-        <is>
-          <t>纯石料前置，后期买几乎无用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="51" customHeight="1">
-      <c r="A22" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>城墙费用 -50%</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>开局村民+1，食物-50；资源持续+15%；步弓手封建/城堡/帝王费用-10/20/30%；胡尔切掷矛兵（掷矛手额外投掷一支长矛）；霍尔坎（鹰勇士生命+40）；城墙费用 -50%</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="inlineStr">
-        <is>
-          <t>圈地与护农，非塔本体。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="81" customHeight="1">
-      <c r="A23" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t>堡垒（城堡攻+4，额外受伤-25%）</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
-        <is>
-          <t>初始木材/食物+50；TC/码头生命+100%，黑暗/封建/城堡/帝王工作速度+5/10/15/20%；城堡时代可用帕提亚战术；帝王可建商队驿站；波斯步弓手（弓兵系消耗额外木材而非黄金）；堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）；骑士系对远程士兵的攻击力 +2</t>
-        </is>
-      </c>
-      <c r="G23" s="22" t="inlineStr">
-        <is>
-          <t>偏城堡，箭塔不吃。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="66" customHeight="1">
-      <c r="A24" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>土堡（城堡工作速度 +25%）</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
-        <is>
-          <t>村民黑暗移速+5%，封建起+10%；马厩单位城堡/帝王费用-15/20%；船舰移速+10%；土堡（团队城堡工作速度+25%）；马格里布骆驼（骆驼每分钟恢复15生命）；从城堡时代开始，靶场提供标枪骑兵</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="inlineStr">
-        <is>
-          <t>偏城堡。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="126" customHeight="1">
-      <c r="A25" s="20" t="n">
-        <v>27</v>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>塔楼提升附近矿工/伐木工效率并作资源存放点</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="inlineStr">
-        <is>
-          <t>精锐掷矛手升级免费；市政/古典掷矛手每分钟回5/10生命；古典解锁战斗操练；任何高地可建除TC外所有建筑；堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点；羊倌/猎人采食时缓慢产金；奥多曼蒂突袭者（步兵/骑兵杀敌获金）；迪亚掠夺者（长矛兵系/征兵系/希腊步兵系/长柄逆刃刀战士摧毁建筑获木/食/金）；贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）；轻装盾兵（掷矛手造成穿透伤害）；建筑的视野 +3</t>
-        </is>
-      </c>
-      <c r="G25" s="22" t="inlineStr">
-        <is>
-          <t>塔的经济外溢，非战力。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="96" customHeight="1">
-      <c r="A26" s="20" t="n">
-        <v>28</v>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>堡垒缓慢产出黄金</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F26" s="22" t="inlineStr">
-        <is>
-          <t>进入市政/古典免费获一军事执政官；村民/捕鱼船存食+10%；古典解锁精锐希腊步兵；希洛人征兵（长矛/掷矛/村民训练+50%）；希腊短剑（附近每5个敌方军事单位，希腊步兵/单列桨座战船攻+1，最大+3）；斯巴达特训（其他希腊步兵附近时希腊步兵+1/+1护甲）；伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）；兵营科技研究速度 +50%</t>
-        </is>
-      </c>
-      <c r="G26" s="22" t="inlineStr">
-        <is>
-          <t>塔的经济外溢。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="81" customHeight="1">
-      <c r="A27" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>摧毁建筑抢夺 25% 资源</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="inlineStr">
-        <is>
-          <t>需主动拆家</t>
-        </is>
-      </c>
-      <c r="F27" s="22" t="inlineStr">
-        <is>
-          <t>捕鱼船/村民存食+5%；摧毁建筑抢25%资源；兵营/攻城武器厂黄金升级-66%；瓦兰吉/维京长船移速+10%；哈马思克（步兵失血时造成更多伤害）；北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）；攻城武器的视野 +2</t>
-        </is>
-      </c>
-      <c r="G27" s="22" t="inlineStr">
-        <is>
-          <t>需要主动进攻拆家才生效。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="51" customHeight="1">
-      <c r="A28" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>马里</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>蛮王（TC 无驻军也能射箭）</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>建筑木材-15%；村民存金+10%；兵营单位封建/城堡/帝王远程护甲+1/+2/+3；蛮王（TC无驻军也能射箭）；死士（骑兵攻击+5）；大学工作速度 +80%</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
-        <is>
-          <t>作用于城镇中心而非塔。</t>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>【阶段4·其他相关】作用于城镇中心而非塔。</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1917,601 +1897,547 @@
       </c>
     </row>
     <row r="2" ht="66" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>撒克逊人</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>塔/城堡城堡起基础箭+100%</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>塔与城堡从城堡时代起发射的基础箭矢 +100%。**注意：官方原版是对 class 52（塔类）通配 +1，而本 mod 把它放大成 +5**——瞭望箭塔系基础箭数只有 1，所以 mod 里这一条会变成 +5 支（威力远大于「翻倍」二字给人的直觉）。单条对塔本体收益最大，但**封建时代无效**，要等城堡时代。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>格鲁吉亚</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>防御工事攻击力 +2，且瞭望箭塔系可造成穿透伤害。全表唯一的塔穿透来源（对成群单位是乘算级收益），且**无时代门槛**，封建即生效。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>射箭孔（瞭望箭塔系可发额外箭矢）</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>瞭望箭塔系可发射额外箭矢。塔基础箭数只有 1，**加 1 支直接翻倍**；无时代门槛、不需驻军，封建塔爆的最强单条。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>凯尔特</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>堡垒（城堡/箭塔攻速+33%；城堡治疗7格内步兵）</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>城堡和瞭望箭塔系攻击速度 +33%，等效 DPS ×1.33；**无时代门槛**、不需任何操作，封建即生效。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>条顿</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>塔驻扎容量+5</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>塔驻扎容量 +5：驻进更多村民就是更多箭。上限最高，但**必须真的驻军**（占用农民 + 操作成本）。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>条顿</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>开垛口（城堡射程+3；驻扎的步兵射箭）</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>城堡射程 +3，且驻扎的步兵会发射箭矢——主要作用于城堡，纯箭塔收益打折。</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>高丽</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>塔升级（瞭望塔→防塔→要塞）与炮塔升级全部免费，省下大量石料；升级炮塔需要化学。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>邑城（瞭望箭塔系射程+2）</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>瞭望箭塔系射程 +2——先手压制对方的塔与城镇中心。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>高丽</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>不列颠</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>邑城（瞭望箭塔系射程+2）</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>瞭望箭塔系射程 +2——先手压制对方的塔与城镇中心。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>瞭望箭塔系攻击力 +2。塔基础箭伤低，+2 的相对占比远高于它给其他兵种的占比。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>不列颠</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>瞭望箭塔系攻击力 +2。塔基础箭伤低，+2 的相对占比远高于它给其他兵种的占比。</t>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>加固堡垒（防御工事每分钟回500生命）</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>防御工事每分钟回复 500 生命值——塔几乎拆不掉，**拆不掉就等于不用重建**。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>女真</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>加固堡垒（防御工事每分钟回500生命）</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>防御工事每分钟回复 500 生命值——塔几乎拆不掉，**拆不掉就等于不用重建**。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>长城（城墙/瞭望箭塔系/炮塔生命+30%）</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>城墙、瞭望箭塔系和炮塔生命值 +30%——抬高血上限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>攻城/防御工事升级木材-75%，研究+100%</t>
+          <t>希腊之火（喷火船射程+1；德罗蒙和炮塔爆炸范围提升）</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>防御工事升级木材费用 -75%、研究速度 +100%，配合上一条形成「便宜又拆不掉」。</t>
+          <t>德罗蒙和炮塔爆炸范围提升；炮塔专属，偏后期。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>建筑黑暗/封建/城堡/帝王生命+10/20/30/40%</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>全建筑生命 +10/20/30/40%，塔作为建筑一并受益。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>土耳其</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>长城（城墙/瞭望箭塔系/炮塔生命+30%）</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>城墙、瞭望箭塔系和炮塔生命值 +30%——抬高血上限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>火炮术（炮塔/手推炮/炮舰射程+2）</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>炮塔、手推炮、炮舰射程 +2；炮塔后期核心火力，但需要先有炮塔。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>拜占庭</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>希腊之火（喷火船射程+1；德罗蒙和炮塔爆炸范围提升）</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>德罗蒙和炮塔爆炸范围提升；炮塔专属，偏后期。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>箭毒（步弓手/防御工事造成中毒伤害）</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>防御工事造成中毒伤害（持续伤害，拆家更稳）；无时代门槛。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>拜占庭</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>塔楼和城堡提供的人口空间 +10</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>塔楼和城堡提供的人口空间 +10，解放前线补农民的房屋位。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>城堡攻击 +4、对冲车/步兵 +3、额外受伤 -25%——**偏城堡，箭塔不吃**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>土堡（团队城堡工作速度+25%）</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>团队城堡工作速度 +25%——偏城堡，箭塔不吃。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>建筑黑暗/封建/城堡/帝王生命+10/20/30/40%</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>全建筑生命 +10/20/30/40%，塔作为建筑一并受益。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>土耳其</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>塔变成经济节点（提速 + 资源存放点），属经济外溢而非战力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>火炮术（炮塔/手推炮/炮舰射程+2）</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>炮塔、手推炮、炮舰射程 +2；炮塔后期核心火力，但需要先有炮塔。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>塔即产金点，属经济外溢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>箭毒（步弓手/防御工事造成中毒伤害）</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>防御工事造成中毒伤害（持续伤害，拆家更稳）；无时代门槛。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>塔楼和城堡提供的人口空间 +10</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>塔楼和城堡提供的人口空间 +10，解放前线补农民的房屋位。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>城堡攻击 +4、对冲车/步兵 +3、额外受伤 -25%——**偏城堡，箭塔不吃**。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>土堡（团队城堡工作速度+25%）</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>团队城堡工作速度 +25%——偏城堡，箭塔不吃。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>堡垒/塔楼提升附近矿工/伐木工效率并作资源存放点</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>塔变成经济节点（提速 + 资源存放点），属经济外溢而非战力。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>伯罗奔尼撒同盟（单列桨座战船系对箭船攻+5，堡垒缓慢产金）</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>塔即产金点，属经济外溢。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>马里</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>蛮王（TC无驻军也能射箭）</t>
         </is>
       </c>
-      <c r="E23" s="19" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>城镇中心无驻军也能射箭——作用于城镇中心而非塔。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E23"/>
+  <autoFilter ref="A1:E21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2523,7 +2449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2563,572 +2489,626 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
+          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>城堡和瞭望塔系 40% 石料费用由木材替代——**直接拆掉箭塔流的头号瓶颈（石料）**，塔的产量上限成倍提高。</t>
+          <t>塔升级（瞭望塔→防塔→要塞）与炮塔升级全部免费，省下大量石料；升级炮塔需要化学。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>攻城/防御工事升级木材-75%，研究+100%</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>防御工事升级木材费用 -75%、研究速度 +100%，配合上一条形成「便宜又拆不掉」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>城堡和瞭望塔系 40% 石料费用由木材替代——**直接拆掉箭塔流的头号瓶颈（石料）**，塔的产量上限成倍提高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>西西里</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>初始石料+100</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>白送一座塔的启动石料。**只在开局有价值，2000 金再买就只剩下面的建造速度了**。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>西西里</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>防御工事建造+50%，TC建造+100%</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>防御工事建造速度 +50%（城镇中心 +100%）——立塔更快，农民暴露时间更短。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>西西里</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>黑暗可建城楼（替瞭望塔系）</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>黑暗时代即可建造城楼，替换瞭望塔系——第一个塔能早很多。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>印加</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>建筑石料-15%</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>建筑石料费用 -15%，塔的建造成本同步下降。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>高丽</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>石矿工速度+20%</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>石矿工工作速度 +20%——石料产能直接抬高（高丽第二条，与「塔升级免费」同卡）。</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>波兰</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>石矿工产石料+黄金</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>石矿工开采石料的同时产出黄金——石料与金币双收，正好支付后续 2000 金/个。</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>普鲁人</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>石矿持续+30%</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>石矿持续时间 +30%——石料总量变多，能支撑更多塔。</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>撒克逊人</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>磨坊/木料/采矿场建成后食物+35，石料+10</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>采矿场建成后食物 +35、石料 +10——小额外快（撒克逊人第二条）。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>撒克逊人</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>修理工的工作速度 +25%</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>修理工工作速度 +25%——塔被打时抢修更快。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>格鲁吉亚</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>建筑修理费用 -25%</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>建筑修理费用 -25%（格鲁吉亚团队加成，对自己生效）——修理更便宜。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>西班牙</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>建筑工速度+30%</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>建筑工速度 +30%——塔立得更快。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>罗马</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>村民收集/建造/修理速度+5%</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>村民收集 / 建造 / 修理速度 +5%——立塔与抢修同时小幅受益。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>埃塞俄比亚</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>哨站视野 +3 且不消耗石料</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>哨站视野 +3 且不消耗石料——前哨网免费铺开，石料全留给箭塔。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>保加利亚</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>TC石料费用-50%</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>城镇中心石料费用 -50%——省下的石料转投塔。</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>保加利亚</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>城堡时代可建营垒</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>城堡时代可建营垒——提供第二种前压工事。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>波希米亚</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>采矿场科技免费</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>采矿场科技免费——采石升级白拿，间接抬高石料产能。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>玛雅</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>城墙费用 -50%</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>城墙费用 -50%——用于圈住前塔与农民。</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>马其顿人</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>哨站可以单独升级为强化哨站</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>哨站可单独升级，前哨网变成战力网。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>马其顿人</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>世界尽头（强化哨站获更高光环和改进属性）</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>强化哨站获得更高的光环加成和改进的属性。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>丹麦人</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>摧毁建筑抢25%资源</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>摧毁建筑抢夺 25% 资源——与塔推拆家形成回收循环，但需主动拆家。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E22"/>
+  <autoFilter ref="A1:E24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3714,7 +3694,7 @@
           <t>弓兵护甲/塔升级免费；邑城（瞭望箭塔系射程+2）；石矿工速度+20%</t>
         </is>
       </c>
-      <c r="E2" s="23" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>**唯一「科技树满分 + 原生塔加成最强」的组合**：整条塔升级链白拿（省下的石料直接变成第二座塔），邑城再给射程 +2，能在对方塔/城镇中心的射程外先手点掉，石矿工 +20% 让石料这个第一瓶颈也一起解决。无短板。</t>
         </is>
@@ -3739,7 +3719,7 @@
           <t>长城（城墙/瞭望箭塔系/炮塔生命+30%）；TC视野+7，人口+15</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>科技树同样满分，长城直接给塔 +30% 生命（塔的血量就是塔推的持续时间）；TC 视野 +7 与人口 +15 都是塔推实用项。没有射程与免费升级，所以排在 高丽 之后。</t>
         </is>
@@ -3764,7 +3744,7 @@
           <t>磨坊/木料/采矿场建成后食物+35、石料+10；塔/城堡从城堡时代起基础箭+100%；修理工速度+25%（团队）</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>**单条收益最大**：基础箭 +100% 是全表最强的塔本体乘区，且**本 mod 把它放大成 class 52 → +5 支箭**（官方原版仅 +1）；另外建采集建筑即送石料、修理工 +25%。唯一风险是**封建时代完全无效**——如果你打的是封建一波塔爆，不要选它当主选。</t>
         </is>
@@ -3789,7 +3769,7 @@
           <t>斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）；建筑修理费用-25%（团队）</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>全表唯一的塔**穿透伤害**：箭会穿过目标继续命中后面聚集的单位，对成群部队是乘算级收益，配合攻 +2 与修理费 -25%，攻防一体。</t>
         </is>
@@ -3814,7 +3794,7 @@
           <t>射箭孔（瞭望箭塔系可发额外箭矢）</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>**封建即生效的最强箭矢来源**：塔基础箭数只有 1，这条直接把箭数翻倍，不需驻军、不需地形。短板是科技树只有 14/17——缺采石场（石料产能）会拖慢塔推节奏，需要靠按钮补石料类条目。</t>
         </is>
@@ -3839,7 +3819,7 @@
           <t>堡垒（城堡和瞭望箭塔系攻击速度+33%）</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>稳定的 ×1.33 DPS，覆盖全部瞭望箭塔系与城堡，无条件、不需操作。缺护腕意味着铁匠铺远程攻击链少一环。</t>
         </is>
@@ -3864,7 +3844,7 @@
           <t>TC驻扎容量+10；塔驻扎容量+5；近射孔/草药免费</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>**理论上限最高的加箭来源**（驻得越多箭越多），但**必须真的投入农民驻守**；不驻军时这条等于没有。</t>
         </is>
@@ -3889,7 +3869,7 @@
           <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>塔基础箭伤只有 5，+2 的相对收益远高于它给其他兵种的收益；同卡还给步弓手 +1 射程，塔推常伴步弓手护塔。</t>
         </is>
@@ -3914,7 +3894,7 @@
           <t>攻城/防御工事升级木材-75%、研究+100%；加固堡垒（防御工事每分回500生命）</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>**拆不掉 = 不用重建**。每分钟回 500 生命意味着对方必须一次性投入足够火力，否则白打；升级降价与提速让整条链更快成型。</t>
         </is>
@@ -3939,7 +3919,7 @@
           <t>火炮术（炮塔/手推炮/炮舰射程+2）；化学免费；火药技术成本-50%</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>**注意：火炮术只作用于炮塔，对瞭望箭塔系无效**。真正的价值是「化学免费」——省下 300 食 200 金的研究，而化学同时给远程防御工事 +1 攻击，是箭塔流也吃的加成。</t>
         </is>
@@ -3964,7 +3944,7 @@
           <t>（无原生塔加成）</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>**隐藏选项**：科技树满分 + 「大学科技 -25%」——大学里正好有箭塔线的射程/攻击/生命/护甲，相当于整条塔升级链打七五折，长期局非常可观；缺点是没有任何直接塔加成，起步全靠按钮。</t>
         </is>
@@ -3989,7 +3969,7 @@
           <t>建筑石料-15%</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>石料是第一瓶颈，-15% 是直给的成本减免；科技树 16/17 也够用。属于「稳但不出彩」。</t>
         </is>
@@ -4014,7 +3994,7 @@
           <t>初始石料+100；黑暗时代可建城楼（替瞭望塔系）；防御工事建造+50%，TC建造+100%</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>**开局爆发最强**：初始石料 +100 直接多一座塔，加建造 +50%。但科技树只有 13/17，且**它没有瞭望箭塔**（用城楼 Donjon 替代），所以所有写「瞭望箭塔系」的加成都吃不到——只有写「防御工事」的才生效。</t>
         </is>
@@ -4039,7 +4019,7 @@
           <t>罗斯堡垒（额外木材替代城堡/瞭望塔系40%石料）</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>**石料瓶颈的唯一解**：40% 石料换成木材后单塔成本大幅下降，早期能立更多塔。但科技树只有 11/17，后期塔的上限明显吃亏；适合「一波流」而非长局。</t>
         </is>
@@ -4064,7 +4044,7 @@
           <t>建筑黑暗/封建/城堡/帝王生命+10/20/30/40%</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>**对塔的血量单笔最大**（帝王 +40%），且作用于全部建筑。科技树 14/17 是短板，缺灼热箭意味着对海军无力。</t>
         </is>
@@ -4089,7 +4069,7 @@
           <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
         </is>
       </c>
-      <c r="E17" s="24" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>与高丽同款的「塔升级免费」，科技树 16/17 也更完整；**但没有邑城射程 +2 与石矿工 +20%**，所以排在高丽之后。若你已经有别的射程来源，它的性价比会跳升。</t>
         </is>
@@ -4114,7 +4094,7 @@
           <t>哨站视野+3 且不消耗石料（团队）</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>**哨站不耗石料**在塔推里很实用（视野网不抢占建塔的石料），科技树 16/17 也高；但没有塔本体的火力/耐久加成。</t>
         </is>
@@ -4139,7 +4119,7 @@
           <t>建筑工速度+30%</t>
         </is>
       </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>立塔速度本身就是塔推的胜负手之一（农民少暴露在野外），科技树 16/17。纯速度型，无火力加成。</t>
         </is>
@@ -4202,90 +4182,90 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>免费位</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="18" t="inlineStr">
         <is>
           <t>射箭孔（瞭望箭塔系可发射额外箭矢）</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="15" t="inlineStr">
         <is>
           <t>塔的**基础箭数只有 1**，这条直接把箭数翻倍。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>格鲁吉亚</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>免费位</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>斯万箭塔（防御工事攻+2；瞭望箭塔系可穿透伤害）</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>全表唯一的塔**穿透伤害**来源：箭会穿过目标继续命中后面排队/聚集的单位，对成群部队是乘算级收益；附带攻 +2，且同卡团队加成建筑修理费 -25%，攻防一体。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>凯尔特</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>免费位</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>堡垒（城堡和瞭望箭塔系攻击速度 +33%）</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>稳定的 ×1.33 DPS，覆盖全部瞭望箭塔系与城堡，不需任何操作。</t>
         </is>
@@ -4302,7 +4282,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -4317,127 +4297,127 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>**付费第一顺位**：一旦进入城堡时代，这是全表最强的塔本体乘区。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="8" t="n">
+          <t>【阶段1·本体强化】**付费第一顺位**：一旦进入城堡时代，这是全表最强的塔本体乘区。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>条顿</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>塔驻扎容量 +5；开垛口</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>把「塔」变成「要塞」——驻满农民后单塔箭数上一个台阶；同卡城堡线拿到射程 +3。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="8" t="n">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>【阶段1·本体强化】把「塔」变成「要塞」——驻满农民后单塔箭数上一个台阶；同卡城堡线拿到射程 +3。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>高丽</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>塔升级免费；邑城（射程+2）；石矿工+20%</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>一卡三吃：升级不花石料、射程 +2 能先手压制对方塔与城镇中心、石料产能 +20%。</t>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>【阶段1·本体强化】一卡三吃：升级不花石料、射程 +2 能先手压制对方塔与城镇中心、石料产能 +20%。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>不列颠</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>英皇侍卫（瞭望箭塔系攻 +2）</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>塔基础箭伤低，+2 的相对收益远高于它给其他兵种的收益。</t>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>【阶段1·本体强化】塔基础箭伤低，+2 的相对收益远高于它给其他兵种的收益。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>女真</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>加固堡垒（防御工事每分钟回 500 生命）；防御工事升级木材-75%、研究+100%</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>**拆不掉 = 不用重建**。</t>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>【阶段1·本体强化】**拆不掉 = 不用重建**。</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4432,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -4467,1595 +4447,1595 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>与上面的回血互为补充：一个加血上限，一个加回复速度。</t>
+          <t>【阶段1·本体强化】与上面的回血互为补充：一个加血上限，一个加回复速度。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>拜占庭</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>2000 金</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>炮塔爆炸范围提升；建筑生命 +40%</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>【阶段1·本体强化】炮塔专属加成 + 全家建筑耐久。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>2000 金</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>防御工事造成中毒伤害；塔/城堡提供人口 +10</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>【阶段1·本体强化】中毒是持续伤害，配合拆家更稳；人口 +10 解放前线补农民的房屋位。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>2000 金</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>罗斯堡垒（40% 石料 → 木材）</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>【阶段2·减费用】石料瓶颈的唯一解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>2000 金</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>建筑石料 -15%</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>【阶段2·减费用】成本类收益，越晚买边际越低。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>2000 金</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>TC 石料 -50%；城堡时代可建营垒</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>【阶段2·减费用】营垒提供第二种前压工事，价值取决于你是否会用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>2000 金</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>城墙费用 -50%</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>【阶段2·减费用】圈地与护农，非塔本体。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>西西里</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>S-</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>防御工事建造 +50%（初始石料已失效）</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>买晚了只剩建造速度，但建造速度本身就是塔推的胜负手之一，仍值 2000 金。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>S-</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>【阶段3·资源效率】买晚了只剩建造速度，但建造速度本身就是塔推的胜负手之一，仍值 2000 金。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>普鲁人</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>罗斯堡垒（40% 石料 → 木材）</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>石料瓶颈的唯一解。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>石矿持续时间 +30%</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>【阶段3·资源效率】前置资源池的扩容，属于「锦上添花」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>2000 金</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>石矿工产石料 + 黄金</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>【阶段3·资源效率】石金双收，但需要你持续采石；塔推通常打不到那么久。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>2000 金</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>建筑工速度 +30%</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>【阶段3·资源效率】与「防御工事建造 +50%」叠加后立塔极快，但单独买收益递减。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>2000 金</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>村民收集/建造/修理速度 +5%</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>【阶段3·资源效率】稳定的小幅乘算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>2000 金</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>哨站视野 +3 且不消耗石料</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>【阶段3·资源效率】侦察与石料节约，锦上添花。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>2000 金</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>采矿场科技免费</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>【阶段3·资源效率】纯石料前置，后期买几乎无用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>土耳其</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>炮塔射程 +2；化学免费</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>进入帝王、有炮塔之后的核心火力升级，属于「后期才有用」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>拜占庭</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>【阶段4·其他相关】进入帝王、有炮塔之后的核心火力升级，属于「后期才有用」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>马其顿人</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
-        <is>
-          <t>炮塔爆炸范围提升；建筑生命 +40%</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>炮塔专属加成 + 全家建筑耐久。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="14" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>哨站可升级为强化哨站；世界尽头</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>【阶段4·其他相关】前哨网变成战力网，战术补充。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E15" s="26" t="inlineStr">
-        <is>
-          <t>防御工事造成中毒伤害；塔/城堡提供人口 +10</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>中毒是持续伤害，配合拆家更稳；人口 +10 解放前线补农民的房屋位。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>堡垒（城堡攻+4，额外受伤-25%）</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>【阶段4·其他相关】偏城堡，箭塔不吃。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
-        <is>
-          <t>建筑石料 -15%</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>成本类收益，越晚买边际越低。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>普鲁人</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>土堡（城堡工作速度 +25%）</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>【阶段4·其他相关】偏城堡。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E17" s="26" t="inlineStr">
-        <is>
-          <t>石矿持续时间 +30%</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>前置资源池的扩容，属于「锦上添花」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>塔楼提升附近矿工/伐木工效率并作资源存放点</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>【阶段4·其他相关】塔的经济外溢，非战力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
-        <is>
-          <t>石矿工产石料 + 黄金</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>石金双收，但需要你持续采石；塔推通常打不到那么久。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>西班牙</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>堡垒缓慢产出黄金</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>【阶段4·其他相关】塔的经济外溢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E19" s="27" t="inlineStr">
-        <is>
-          <t>建筑工速度 +30%</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>与「防御工事建造 +50%」叠加后立塔极快，但单独买收益递减。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>摧毁建筑抢夺 25% 资源</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>【阶段4·其他相关】需要主动进攻拆家才生效。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E20" s="27" t="inlineStr">
-        <is>
-          <t>村民收集/建造/修理速度 +5%</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>稳定的小幅乘算。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>2000 金</t>
-        </is>
-      </c>
-      <c r="E21" s="27" t="inlineStr">
-        <is>
-          <t>哨站视野 +3 且不消耗石料</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>侦察与石料节约，锦上添花。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>马其顿人</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>2000 金</t>
-        </is>
-      </c>
-      <c r="E22" s="27" t="inlineStr">
-        <is>
-          <t>哨站可升级为强化哨站；世界尽头</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>前哨网变成战力网，战术补充。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="17" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>2000 金</t>
-        </is>
-      </c>
-      <c r="E23" s="27" t="inlineStr">
-        <is>
-          <t>TC 石料 -50%；城堡时代可建营垒</t>
-        </is>
-      </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>营垒提供第二种前压工事，价值取决于你是否会用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>2000 金</t>
-        </is>
-      </c>
-      <c r="E24" s="27" t="inlineStr">
-        <is>
-          <t>采矿场科技免费</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>纯石料前置，后期买几乎无用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>2000 金</t>
-        </is>
-      </c>
-      <c r="E25" s="27" t="inlineStr">
-        <is>
-          <t>城墙费用 -50%</t>
-        </is>
-      </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>圈地与护农，非塔本体。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>蛮王（TC 无驻军也能射箭）</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>【阶段4·其他相关】作用于城镇中心而非塔。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>2000 金</t>
-        </is>
-      </c>
-      <c r="E26" s="28" t="inlineStr">
-        <is>
-          <t>堡垒（城堡攻+4，额外受伤-25%）</t>
-        </is>
-      </c>
-      <c r="F26" s="22" t="inlineStr">
-        <is>
-          <t>偏城堡，箭塔不吃。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>不建议</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>无一条直接加强塔本体或其石料/建造</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>木栅栏生命值 +33%——唯一沾「防御工事」边的，但木栅栏不是塔，2000 金不值</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>2000 金</t>
-        </is>
-      </c>
-      <c r="E27" s="28" t="inlineStr">
-        <is>
-          <t>土堡（城堡工作速度 +25%）</t>
-        </is>
-      </c>
-      <c r="F27" s="22" t="inlineStr">
-        <is>
-          <t>偏城堡。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="20" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>不建议</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>无一条直接加强塔本体或其石料/建造</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>无需建筑即可升时代、解锁建筑——建筑机制，与塔的强度无关</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>吴</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>2000 金</t>
-        </is>
-      </c>
-      <c r="E28" s="28" t="inlineStr">
-        <is>
-          <t>塔楼提升附近矿工/伐木工效率并作资源存放点</t>
-        </is>
-      </c>
-      <c r="F28" s="22" t="inlineStr">
-        <is>
-          <t>塔的经济外溢，非战力。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="20" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>不建议</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>无一条直接加强塔本体或其石料/建造</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>房屋建造速度 +100%——建造速度只作用于房屋，不含防御工事</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>阿契美尼德</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
-        <is>
-          <t>2000 金</t>
-        </is>
-      </c>
-      <c r="E29" s="28" t="inlineStr">
-        <is>
-          <t>堡垒缓慢产出黄金</t>
-        </is>
-      </c>
-      <c r="F29" s="22" t="inlineStr">
-        <is>
-          <t>塔的经济外溢。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>不建议</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>无一条直接加强塔本体或其石料/建造</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>房屋建造速度 +100%——同上，且古典模式，与箭塔流无交集</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>匈奴</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
-        <is>
-          <t>2000 金</t>
-        </is>
-      </c>
-      <c r="E30" s="28" t="inlineStr">
-        <is>
-          <t>摧毁建筑抢夺 25% 资源</t>
-        </is>
-      </c>
-      <c r="F30" s="22" t="inlineStr">
-        <is>
-          <t>需要主动进攻拆家才生效。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>马里</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>不建议</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>无一条直接加强塔本体或其石料/建造</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>不需要房屋（初始木材 -100）——省木材，但省下的不是石料，对塔无直接帮助</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
-        <is>
-          <t>2000 金</t>
-        </is>
-      </c>
-      <c r="E31" s="28" t="inlineStr">
-        <is>
-          <t>蛮王（TC 无驻军也能射箭）</t>
-        </is>
-      </c>
-      <c r="F31" s="22" t="inlineStr">
-        <is>
-          <t>作用于城镇中心而非塔。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="20" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>库曼</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>不建议</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>无一条直接加强塔本体或其石料/建造</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>游牧（失去房屋人口不减）——人口机制，与塔无关</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E32" s="28" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
-        <is>
-          <t>木栅栏生命值 +33%——唯一沾「防御工事」边的，但木栅栏不是塔，2000 金不值</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="20" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="20" t="inlineStr">
-        <is>
-          <t>高棉</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>村民/僧侣所占人口 -10%——人口机制</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>缅甸</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D39" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E33" s="28" t="inlineStr">
+      <c r="E39" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
-        <is>
-          <t>无需建筑即可升时代、解锁建筑——建筑机制，与塔的强度无关</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t>吴</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>伐木场科技免费——木材经济，与塔的石料无关</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D34" s="20" t="inlineStr">
+      <c r="D40" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E34" s="28" t="inlineStr">
+      <c r="E40" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
-        <is>
-          <t>房屋建造速度 +100%——建造速度只作用于房屋，不含防御工事</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="20" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="20" t="inlineStr">
-        <is>
-          <t>阿契美尼德</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="inlineStr">
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>码头提供的人口空间 +5——海军人口，与塔无关</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>萨拉森</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr">
+      <c r="D41" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E35" s="28" t="inlineStr">
+      <c r="E41" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
-        <is>
-          <t>房屋建造速度 +100%——同上，且古典模式，与箭塔流无交集</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="20" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>匈奴</t>
-        </is>
-      </c>
-      <c r="C36" s="20" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t>市场木材 -100——木材经济；另有投石车与步弓加成，均非塔</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>立陶宛</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D36" s="20" t="inlineStr">
+      <c r="D42" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E36" s="28" t="inlineStr">
+      <c r="E42" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
-        <is>
-          <t>不需要房屋（初始木材 -100）——省木材，但省下的不是石料，对塔无直接帮助</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="20" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="20" t="inlineStr">
-        <is>
-          <t>蒙古</t>
-        </is>
-      </c>
-      <c r="C37" s="20" t="inlineStr">
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>塔盾（长矛/掷矛远程护甲 +2）——名称带「塔」但是盾牌科技，与箭塔无关</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="21" t="inlineStr">
+        <is>
+          <t>雅典</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D37" s="20" t="inlineStr">
+      <c r="D43" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E37" s="28" t="inlineStr">
+      <c r="E43" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
-        <is>
-          <t>游牧（失去房屋人口不减）——人口机制，与塔无关</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="20" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>孟加拉</t>
-        </is>
-      </c>
-      <c r="C38" s="20" t="inlineStr">
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>伐木工缓慢产食——经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="21" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>穆伊斯卡</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D38" s="20" t="inlineStr">
+      <c r="D44" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E38" s="28" t="inlineStr">
+      <c r="E44" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F38" s="22" t="inlineStr">
-        <is>
-          <t>村民/僧侣所占人口 -10%——人口机制</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="20" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="20" t="inlineStr">
-        <is>
-          <t>缅甸</t>
-        </is>
-      </c>
-      <c r="C39" s="20" t="inlineStr">
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>蔷琵战士/靶场护甲——兵种</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D39" s="20" t="inlineStr">
+      <c r="D45" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E39" s="28" t="inlineStr">
+      <c r="E45" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F39" s="22" t="inlineStr">
-        <is>
-          <t>伐木场科技免费——木材经济，与塔的石料无关</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="20" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="20" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C40" s="20" t="inlineStr">
+      <c r="F45" s="23" t="inlineStr">
+        <is>
+          <t>经济升级无木材、伐木工产金——经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D40" s="20" t="inlineStr">
+      <c r="D46" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E40" s="28" t="inlineStr">
+      <c r="E46" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F40" s="22" t="inlineStr">
-        <is>
-          <t>码头提供的人口空间 +5——海军人口，与塔无关</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="20" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="20" t="inlineStr">
-        <is>
-          <t>萨拉森</t>
-        </is>
-      </c>
-      <c r="C41" s="20" t="inlineStr">
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>伐木工产木+食物——经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="21" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D41" s="20" t="inlineStr">
+      <c r="D47" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E41" s="28" t="inlineStr">
+      <c r="E47" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F41" s="22" t="inlineStr">
-        <is>
-          <t>市场木材 -100——木材经济；另有投石车与步弓加成，均非塔</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="20" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="20" t="inlineStr">
-        <is>
-          <t>立陶宛</t>
-        </is>
-      </c>
-      <c r="C42" s="20" t="inlineStr">
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>采果工产食+木材、船舰生命——经济与海军</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="21" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D42" s="20" t="inlineStr">
+      <c r="D48" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E42" s="28" t="inlineStr">
+      <c r="E48" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F42" s="22" t="inlineStr">
-        <is>
-          <t>塔盾（长矛/掷矛远程护甲 +2）——名称带「塔」但是盾牌科技，与箭塔无关</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="20" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="20" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="C43" s="20" t="inlineStr">
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>步兵/投石手/掷矛生命、敌方城堡可见——兵种与侦察</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="21" t="inlineStr">
+        <is>
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D43" s="20" t="inlineStr">
+      <c r="D49" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E43" s="28" t="inlineStr">
+      <c r="E49" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F43" s="22" t="inlineStr">
-        <is>
-          <t>伐木工缓慢产食——经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="20" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="20" t="inlineStr">
-        <is>
-          <t>穆伊斯卡</t>
-        </is>
-      </c>
-      <c r="C44" s="20" t="inlineStr">
+      <c r="F49" s="23" t="inlineStr">
+        <is>
+          <t>城堡时代可升重装骑士——兵种</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="21" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>鞑靼</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D44" s="20" t="inlineStr">
+      <c r="D50" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E44" s="28" t="inlineStr">
+      <c r="E50" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F44" s="22" t="inlineStr">
-        <is>
-          <t>蔷琵战士/靶场护甲——兵种</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="20" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>越南</t>
-        </is>
-      </c>
-      <c r="C45" s="20" t="inlineStr">
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>新建 TC 产绵羊、巨型投石机射程——经济与攻城</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="21" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D45" s="20" t="inlineStr">
+      <c r="D51" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E45" s="28" t="inlineStr">
+      <c r="E51" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F45" s="22" t="inlineStr">
-        <is>
-          <t>经济升级无木材、伐木工产金——经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="20" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="20" t="inlineStr">
-        <is>
-          <t>蜀</t>
-        </is>
-      </c>
-      <c r="C46" s="20" t="inlineStr">
+      <c r="F51" s="23" t="inlineStr">
+        <is>
+          <t>骑兵生命、城堡费用 -15/25%——兵种与城堡成本（不降塔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="21" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="21" t="inlineStr">
+        <is>
+          <t>哥特</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D46" s="20" t="inlineStr">
+      <c r="D52" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E46" s="28" t="inlineStr">
+      <c r="E52" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F46" s="22" t="inlineStr">
-        <is>
-          <t>伐木工产木+食物——经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="20" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="20" t="inlineStr">
-        <is>
-          <t>葡萄牙</t>
-        </is>
-      </c>
-      <c r="C47" s="20" t="inlineStr">
+      <c r="F52" s="23" t="inlineStr">
+        <is>
+          <t>步兵费用与对建筑攻击——兵种</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="21" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="21" t="inlineStr">
+        <is>
+          <t>马来</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D47" s="20" t="inlineStr">
+      <c r="D53" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E47" s="28" t="inlineStr">
+      <c r="E53" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F47" s="22" t="inlineStr">
-        <is>
-          <t>采果工产食+木材、船舰生命——经济与海军</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="20" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="20" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C48" s="20" t="inlineStr">
+      <c r="F53" s="23" t="inlineStr">
+        <is>
+          <t>象兵费用——兵种</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D48" s="20" t="inlineStr">
+      <c r="D54" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E48" s="28" t="inlineStr">
+      <c r="E54" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F48" s="22" t="inlineStr">
-        <is>
-          <t>步兵/投石手/掷矛生命、敌方城堡可见——兵种与侦察</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="20" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="20" t="inlineStr">
-        <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C49" s="20" t="inlineStr">
+      <c r="F54" s="23" t="inlineStr">
+        <is>
+          <t>村民杀狼、斥候费用、近战升级免费——兵种</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="21" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D49" s="20" t="inlineStr">
+      <c r="D55" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E49" s="28" t="inlineStr">
+      <c r="E55" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F49" s="22" t="inlineStr">
-        <is>
-          <t>城堡时代可升重装骑士——兵种</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="20" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="20" t="inlineStr">
-        <is>
-          <t>鞑靼</t>
-        </is>
-      </c>
-      <c r="C50" s="20" t="inlineStr">
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>重装骑射手升级成本 -50%——兵种</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="21" t="inlineStr">
+        <is>
+          <t>瞿折罗</t>
+        </is>
+      </c>
+      <c r="C56" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D50" s="20" t="inlineStr">
+      <c r="D56" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E50" s="28" t="inlineStr">
+      <c r="E56" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F50" s="22" t="inlineStr">
-        <is>
-          <t>新建 TC 产绵羊、巨型投石机射程——经济与攻城</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="20" t="inlineStr">
-        <is>
-          <t>法兰克</t>
-        </is>
-      </c>
-      <c r="C51" s="20" t="inlineStr">
+      <c r="F56" s="23" t="inlineStr">
+        <is>
+          <t>骑兵额外伤害——兵种</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="21" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="21" t="inlineStr">
+        <is>
+          <t>瓦兰吉人</t>
+        </is>
+      </c>
+      <c r="C57" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D51" s="20" t="inlineStr">
+      <c r="D57" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E51" s="28" t="inlineStr">
+      <c r="E57" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F51" s="22" t="inlineStr">
-        <is>
-          <t>骑兵生命、城堡费用 -15/25%——兵种与城堡成本（不降塔）</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="20" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="20" t="inlineStr">
-        <is>
-          <t>哥特</t>
-        </is>
-      </c>
-      <c r="C52" s="20" t="inlineStr">
+      <c r="F57" s="23" t="inlineStr">
+        <is>
+          <t>维京长船/大型投石战舰攻速——海军</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="21" t="inlineStr">
+        <is>
+          <t>维京</t>
+        </is>
+      </c>
+      <c r="C58" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D52" s="20" t="inlineStr">
+      <c r="D58" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E52" s="28" t="inlineStr">
+      <c r="E58" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F52" s="22" t="inlineStr">
-        <is>
-          <t>步兵费用与对建筑攻击——兵种</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="20" t="inlineStr">
-        <is>
-          <t>马来</t>
-        </is>
-      </c>
-      <c r="C53" s="20" t="inlineStr">
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>步兵生命、战船费用——兵种与海军</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="21" t="inlineStr">
+        <is>
+          <t>魏</t>
+        </is>
+      </c>
+      <c r="C59" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D53" s="20" t="inlineStr">
+      <c r="D59" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E53" s="28" t="inlineStr">
+      <c r="E59" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F53" s="22" t="inlineStr">
-        <is>
-          <t>象兵费用——兵种</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="20" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="20" t="inlineStr">
-        <is>
-          <t>马扎尔</t>
-        </is>
-      </c>
-      <c r="C54" s="20" t="inlineStr">
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>黑光铠/鲜卑掠骑兵生命、牵引抛石机费用——兵种与攻城</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="21" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="21" t="inlineStr">
+        <is>
+          <t>亚美尼亚</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D54" s="20" t="inlineStr">
+      <c r="D60" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E54" s="28" t="inlineStr">
+      <c r="E60" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F54" s="22" t="inlineStr">
-        <is>
-          <t>村民杀狼、斥候费用、近战升级免费——兵种</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="20" t="inlineStr">
-        <is>
-          <t>契丹</t>
-        </is>
-      </c>
-      <c r="C55" s="20" t="inlineStr">
+      <c r="F60" s="23" t="inlineStr">
+        <is>
+          <t>步兵生命、牧师战士治疗——兵种</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="21" t="inlineStr">
+        <is>
+          <t>意大利</t>
+        </is>
+      </c>
+      <c r="C61" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D55" s="20" t="inlineStr">
+      <c r="D61" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E55" s="28" t="inlineStr">
+      <c r="E61" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F55" s="22" t="inlineStr">
-        <is>
-          <t>重装骑射手升级成本 -50%——兵种</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="20" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="20" t="inlineStr">
-        <is>
-          <t>瞿折罗</t>
-        </is>
-      </c>
-      <c r="C56" s="20" t="inlineStr">
+      <c r="F61" s="23" t="inlineStr">
+        <is>
+          <t>意大利佣兵、佣兵费用——兵种</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="21" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="21" t="inlineStr">
+        <is>
+          <t>印度斯坦</t>
+        </is>
+      </c>
+      <c r="C62" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D56" s="20" t="inlineStr">
+      <c r="D62" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E56" s="28" t="inlineStr">
+      <c r="E62" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F56" s="22" t="inlineStr">
-        <is>
-          <t>骑兵额外伤害——兵种</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="20" t="inlineStr">
-        <is>
-          <t>瓦兰吉人</t>
-        </is>
-      </c>
-      <c r="C57" s="20" t="inlineStr">
+      <c r="F62" s="23" t="inlineStr">
+        <is>
+          <t>村民费用、斥候与骆驼对建筑攻击——经济与兵种</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="21" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="21" t="inlineStr">
+        <is>
+          <t>阿兹特克</t>
+        </is>
+      </c>
+      <c r="C63" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D57" s="20" t="inlineStr">
+      <c r="D63" s="21" t="inlineStr">
         <is>
           <t>不建议</t>
         </is>
       </c>
-      <c r="E57" s="28" t="inlineStr">
+      <c r="E63" s="22" t="inlineStr">
         <is>
           <t>无一条直接加强塔本体或其石料/建造</t>
         </is>
       </c>
-      <c r="F57" s="22" t="inlineStr">
-        <is>
-          <t>维京长船/大型投石战舰攻速——海军</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="20" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="20" t="inlineStr">
-        <is>
-          <t>维京</t>
-        </is>
-      </c>
-      <c r="C58" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D58" s="20" t="inlineStr">
-        <is>
-          <t>不建议</t>
-        </is>
-      </c>
-      <c r="E58" s="28" t="inlineStr">
-        <is>
-          <t>无一条直接加强塔本体或其石料/建造</t>
-        </is>
-      </c>
-      <c r="F58" s="22" t="inlineStr">
-        <is>
-          <t>步兵生命、战船费用——兵种与海军</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="20" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="20" t="inlineStr">
-        <is>
-          <t>魏</t>
-        </is>
-      </c>
-      <c r="C59" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D59" s="20" t="inlineStr">
-        <is>
-          <t>不建议</t>
-        </is>
-      </c>
-      <c r="E59" s="28" t="inlineStr">
-        <is>
-          <t>无一条直接加强塔本体或其石料/建造</t>
-        </is>
-      </c>
-      <c r="F59" s="22" t="inlineStr">
-        <is>
-          <t>黑光铠/鲜卑掠骑兵生命、牵引抛石机费用——兵种与攻城</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="20" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="20" t="inlineStr">
-        <is>
-          <t>亚美尼亚</t>
-        </is>
-      </c>
-      <c r="C60" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D60" s="20" t="inlineStr">
-        <is>
-          <t>不建议</t>
-        </is>
-      </c>
-      <c r="E60" s="28" t="inlineStr">
-        <is>
-          <t>无一条直接加强塔本体或其石料/建造</t>
-        </is>
-      </c>
-      <c r="F60" s="22" t="inlineStr">
-        <is>
-          <t>步兵生命、牧师战士治疗——兵种</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="20" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="20" t="inlineStr">
-        <is>
-          <t>意大利</t>
-        </is>
-      </c>
-      <c r="C61" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D61" s="20" t="inlineStr">
-        <is>
-          <t>不建议</t>
-        </is>
-      </c>
-      <c r="E61" s="28" t="inlineStr">
-        <is>
-          <t>无一条直接加强塔本体或其石料/建造</t>
-        </is>
-      </c>
-      <c r="F61" s="22" t="inlineStr">
-        <is>
-          <t>意大利佣兵、佣兵费用——兵种</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="20" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="20" t="inlineStr">
-        <is>
-          <t>印度斯坦</t>
-        </is>
-      </c>
-      <c r="C62" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D62" s="20" t="inlineStr">
-        <is>
-          <t>不建议</t>
-        </is>
-      </c>
-      <c r="E62" s="28" t="inlineStr">
-        <is>
-          <t>无一条直接加强塔本体或其石料/建造</t>
-        </is>
-      </c>
-      <c r="F62" s="22" t="inlineStr">
-        <is>
-          <t>村民费用、斥候与骆驼对建筑攻击——经济与兵种</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="20" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="20" t="inlineStr">
-        <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C63" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D63" s="20" t="inlineStr">
-        <is>
-          <t>不建议</t>
-        </is>
-      </c>
-      <c r="E63" s="28" t="inlineStr">
-        <is>
-          <t>无一条直接加强塔本体或其石料/建造</t>
-        </is>
-      </c>
-      <c r="F63" s="22" t="inlineStr">
+      <c r="F63" s="23" t="inlineStr">
         <is>
           <t>修道院科技后僧侣生命 +5——僧侣</t>
         </is>
@@ -6074,7 +6054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6082,120 +6062,120 @@
   </cols>
   <sheetData>
     <row r="1" ht="49" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>《帝国时代2 决定版》箭塔流 —— 62 按钮最优选择顺序（纯塔强化版）</t>
         </is>
       </c>
-      <c r="B1" s="30" t="inlineStr"/>
+      <c r="B1" s="25" t="inlineStr"/>
     </row>
     <row r="2" ht="19" customHeight="1">
-      <c r="A2" s="31" t="inlineStr"/>
-      <c r="B2" s="30" t="inlineStr"/>
+      <c r="A2" s="26" t="inlineStr"/>
+      <c r="B2" s="25" t="inlineStr"/>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>模组机制（用户提供）</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>「文明联盟」模组中 62 个科技按钮各代表一个文明的全部特性（含独特科技，不含独特单位）；开局只能选 3 个，之后每多选 1 个花费 2000 金。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>本表口径</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>只收录直接作用于「塔 / 防御工事」的条目，拆成两类：甲类 = 塔本体强化（火力 / 耐久 / 功能）；乙类 = 塔的直接前置（石料 / 建造成本 / 建造速度 / 修理）。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="31" t="inlineStr"/>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr"/>
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>泛经济与人口类（村民携带量、房屋、兵种费用、骑射攻防、贸易等）已全部剔除；与该范围无关的文明单独列在「与箭塔无关·可跳过」页，帮你省下 2000 金/个。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
-      <c r="A6" s="31" t="inlineStr"/>
-      <c r="B6" s="30" t="inlineStr"/>
+      <c r="A6" s="26" t="inlineStr"/>
+      <c r="B6" s="25" t="inlineStr"/>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>三条判断准则</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>① **箭数 &gt; 攻速 &gt; 攻击力**：塔基础箭数只有 1、箭伤很低，「多一支箭」在多数情况下约等于「多一倍输出」；攻速 +33% 是稳定的 ×1.33；攻击力 +2 的相对收益最小（格鲁吉亚的穿透除外，属另一量级）。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="31" t="inlineStr"/>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr"/>
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>② **优先「无条件」，其次「需操作」**：日本（额外箭矢）、格鲁吉亚（穿透）、凯尔特（攻速）都不需驻军、不需地形、不需前置，封建时代立刻生效；条顿（驻扎容量 +5）理论上限更高，但必须真的派农民驻守。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="31" t="inlineStr"/>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr"/>
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>③ **开局专属效果必须放进免费位**：全部 450 条里带「初始 / 开局」且与塔相关的只有西西里的「初始石料 +100」——这类效果买晚了会失效，若要用它就必须占一个免费位。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="31" t="inlineStr"/>
-      <c r="B10" s="30" t="inlineStr"/>
+      <c r="A10" s="26" t="inlineStr"/>
+      <c r="B10" s="25" t="inlineStr"/>
     </row>
     <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>★ 最重要的一条时代提醒</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>撒克逊人的「塔和城堡从城堡时代开始，发射的基础箭矢 +100%」是**全表最强的塔本体乘区，但封建时代完全没有效果**。另外它在 dat 里写的是 class 52（塔类）通配，而**本 mod 把官方的 +1 放大成了 +5**（城堡 +20）：瞭望箭塔系基础箭数只有 1，所以 mod 内实际是 +5 支箭，而不是字面上的「翻倍」。如果你打的是封建一波塔爆，不要把它放免费位；如果你确定能进城堡时代（2000 金/个的机制说明这是长局），它应当排在付费第 1 位、甚至顶掉免费位的第 ③ 名。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="31" t="inlineStr"/>
-      <c r="B12" s="30" t="inlineStr"/>
+      <c r="A12" s="26" t="inlineStr"/>
+      <c r="B12" s="25" t="inlineStr"/>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>免费 3 位结论</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>① 日本 ② 格鲁吉亚 ③ 凯尔特 —— 三条都是「无时代门槛 + 无条件 + 不需操作」的箭矢/攻速来源，封建即成型。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>替换规则</t>
         </is>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>· 能进城堡时代 → 第 ③ 位（凯尔特）换成 撒克逊人
 · 塔立不起来 / 太慢 → 第 ③ 位换成 西西里（初始石料 +100）
@@ -6203,205 +6183,232 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
+    <row r="15" ht="79" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>排序口径（四阶段）</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>本表按打法口径分四个阶段排序：先加强塔本体，再减它的建造成本，最后才补石料效率。
+① 阶段 1 · 本体强化 = 直接加强塔 / 防御工事本体的条目（箭数 / 攻速 / 攻击 / 射程 / 生命 / 回血 / 驻扎）。
+② 阶段 2 · 减费用 = 降低塔及同系防御工事的建造 / 升级费用的条目（石料替代、建筑石料 -N%、升级免费）。
+③ 阶段 3 · 资源效率 = 石料产能与采集 / 建造效率（石矿工、采石、建筑工速度、村民效率）。
+④ 阶段 4 · 其他相关 = 偏城堡、经济外溢、需主动操作，或只作用于城镇中心的条目（列出来避免误买）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>付费顺序要点</t>
         </is>
       </c>
-      <c r="B15" s="30" t="inlineStr">
-        <is>
-          <t>第 4 顺位起：撒克逊人（城堡线最强）→ 条顿 → 高丽 → 不列颠 → 女真 → 中国，前 9 位基本都是甲类；第 10 顺位起转为乙类与后期项（西西里 → 斯拉夫 → 火炮术…）；25 顺位之后基本只为收集，实战可停。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="31" t="inlineStr"/>
-      <c r="B16" s="30" t="inlineStr"/>
-    </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>第 4 顺位起全部是阶段 1（本体强化）：撒克逊人 → 条顿 → 高丽 → 不列颠 → 女真 → 中国 → 拜占庭 → 图皮；
+接着是阶段 2 减费用（斯拉夫 → 印加 → 保加利亚 → 玛雅）；
+再到阶段 3 石料效率（西西里 → 普鲁人 → 波兰 → 西班牙 → 罗马 → 埃塞俄比亚 → 波希米亚）；
+最后阶段 4（炮塔向的土耳其、偏城堡的波斯/柏柏尔、经济外溢、作用于 TC 等）基本只为收集，实战可停。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="26" t="inlineStr"/>
+      <c r="B17" s="25" t="inlineStr"/>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>★ 先定主选文明，再挑 3 个免费位</t>
         </is>
       </c>
-      <c r="B17" s="30" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>模组里「主选文明」自带的加成是免费的，而按钮每个都要花钱（开局 3 个免费位之后 2000 金/个）。所以正确流程是：**先在「主选文明推荐」页挑一个自带塔加成的文明，再用 3 个免费位补它的缺口**，而不是反过来。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="49" customHeight="1">
-      <c r="A18" s="31" t="inlineStr">
+    <row r="19" ht="49" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>主选文明怎么挑</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>看两件事：① **原生塔/防御工事加成**（越多、越直接，起步越快）；② **箭塔线科技树完整度**（满分 17 项：化学、砖石建筑、建筑学、灼热箭、箭孔、杀兵孔、弹道学、防卫塔、大型箭塔、强化城墙、采石、采石场、城镇瞭望、城镇巡逻、制箭术、锥形箭、护腕；越全，后期上限越高）。推荐页按「原生加成强度」排，科技树完整度作为参考列在同一行。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="31" t="inlineStr"/>
-      <c r="B19" s="30" t="inlineStr">
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="26" t="inlineStr"/>
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>**最稳的两个选择是 15 高丽 与 56 中国**——都同时拿到 17/17 满分科技树与实打实的塔加成（高丽免费升级链+射程+2，中国塔血+30%），几乎没有短板。</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="31" t="inlineStr"/>
-      <c r="B20" s="30" t="inlineStr">
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="26" t="inlineStr"/>
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>**49 西西里 要特别当心**：它是全表唯一没有瞭望箭塔的文明（用城楼 Donjon 替代），所以一切写「瞭望箭塔系 / 箭塔」的加成对它全部无效，只有写「防御工事」的才生效。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="31" t="inlineStr"/>
-      <c r="B21" s="30" t="inlineStr"/>
-    </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="31" t="inlineStr">
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="26" t="inlineStr"/>
+      <c r="B22" s="25" t="inlineStr"/>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>★ 最重要的一条：别买重复</t>
         </is>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>主选文明已经自带的加成，**不要再用按钮买一遍**。一个按钮只能研究一次，重复购买等于白花 2000 金。例：主选 高丽 之后，「弓兵护甲/塔升级免费」这个按钮对你就是零收益；主选 中国 之后不要买长城。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="31" t="inlineStr"/>
-      <c r="B23" s="30" t="inlineStr"/>
-    </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="31" t="inlineStr">
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="26" t="inlineStr"/>
+      <c r="B24" s="25" t="inlineStr"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>模组专属：塔类联动（来自模组自带文本）</t>
         </is>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>★「结盟中国 + 高丽 + 日本」三个按钮同时点满 → 额外奖励「塔类远防 +200」。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="31" t="inlineStr"/>
-      <c r="B25" s="30" t="inlineStr">
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="26" t="inlineStr"/>
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>这条只写在「高丽」与「日本」两个按钮的说明里，中国按钮上不显示，最容易漏。</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="31" t="inlineStr"/>
-      <c r="B26" s="30" t="inlineStr">
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="26" t="inlineStr"/>
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>它写的是「塔类」，含瞭望箭塔系与炮塔；+200 远防意味着塔几乎免疫弓箭/箭塔，只剩攻城武器与近战能拆。</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="31" t="inlineStr"/>
-      <c r="B27" s="30" t="inlineStr">
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="26" t="inlineStr"/>
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>「塔防SSR」按钮：塔类与城堡攻速 ×2，但与「攻城SSR」互斥（二选一），做塔就选它。</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="31" t="inlineStr"/>
-      <c r="B28" s="30" t="inlineStr">
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="26" t="inlineStr"/>
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>「切换贸易获取 50% 的石头」：模组内唯一的持续石材产出，塔海战术的经济支撑。</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="31" t="inlineStr"/>
-      <c r="B29" s="30" t="inlineStr"/>
-    </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="31" t="inlineStr">
-        <is>
-          <t>档位含义</t>
-        </is>
-      </c>
-      <c r="B30" s="30" t="inlineStr">
-        <is>
-          <t>S = 塔本体质变；S- = 前置关键但买晚边际下降；A = 显著强化；B = 有用但偏后期或偏成本；C = 战术补充；D = 与塔本体关系弱（列出来避免你误买）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="31" t="inlineStr"/>
-      <c r="B31" s="30" t="inlineStr"/>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="26" t="inlineStr"/>
+      <c r="B30" s="25" t="inlineStr"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>档位含义（与其余 13 张流派表同一套规则）</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>S = 前 3 名（免费位）；A = 第 4–8 名；B = 第 9–18 名；C = 第 19–30 名；D = 第 31 名以后（与塔本体关系弱，列出来避免你误买）。</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="31" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr"/>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>注意：档位只反映名次区间，真正的依据是上面的「四阶段排序」——阶段 1（本体强化）永远优先于阶段 2/3。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="26" t="inlineStr"/>
+      <c r="B33" s="25" t="inlineStr"/>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>未验证项（重要，请实测）</t>
         </is>
       </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>① 各效果的叠加方式（加算 / 乘算、能否与自选基础文明叠加）未经实测；档位是按官方文字推算的相对排序，不是精确数值。</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="64" customHeight="1">
-      <c r="A33" s="31" t="inlineStr"/>
-      <c r="B33" s="30" t="inlineStr">
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="26" t="inlineStr"/>
+      <c r="B35" s="25" t="inlineStr">
         <is>
           <t>② 「基础箭矢 +100%」（撒克逊人）与「发射额外箭矢」（日本）是否叠加、叠加后箭数上限多少，需在游戏内确认；若二者不叠加，免费第 ③ 位应直接改选 撒克逊人 或 西西里。另外撒克逊这条在 mod 里是 class 52 → 属性 102/107 各 +5（官方原版为 +1），而炮塔的 102 基础值是 0、靠引擎保底射 1 发——所以该条对炮塔的效果（+5 后实际几发）属 dat 语义推断，同样需实测。</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="31" t="inlineStr"/>
-      <c r="B34" s="30" t="inlineStr">
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="26" t="inlineStr"/>
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>③ 每个按钮的研究成本（2000 金）与耗时是否随次数递增未知；本表按固定 2000 金/个给出顺序。</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="31" t="inlineStr"/>
-      <c r="B35" s="30" t="inlineStr">
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="26" t="inlineStr"/>
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>④ 表中未收录独特单位（按用户要求排除）。</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="31" t="inlineStr"/>
-      <c r="B36" s="30" t="inlineStr"/>
-    </row>
-    <row r="37" ht="19" customHeight="1">
-      <c r="A37" s="31" t="inlineStr">
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="26" t="inlineStr"/>
+      <c r="B38" s="25" t="inlineStr"/>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
         <is>
           <t>数据来源</t>
         </is>
       </c>
-      <c r="B37" s="30" t="inlineStr">
+      <c r="B39" s="25" t="inlineStr">
         <is>
           <t>用户提供的 62 张文明卡片 PNG（By RemonBo）逐字整理，并经游戏官方简中字串交叉校验。</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="19" customHeight="1">
-      <c r="A38" s="31" t="inlineStr">
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
         <is>
           <t>整理</t>
         </is>
       </c>
-      <c r="B38" s="30" t="inlineStr">
+      <c r="B40" s="25" t="inlineStr">
         <is>
           <t>By RemonBo；本表由 DSH 生成。</t>
         </is>
